--- a/AAII_Financials/Yearly/CSW_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CSW_YR_FIN.xlsx
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>628900</v>
+        <v>627500</v>
       </c>
       <c r="E9" s="3">
         <v>485000</v>
@@ -771,7 +771,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>453700</v>
+        <v>455100</v>
       </c>
       <c r="E10" s="3">
         <v>393300</v>
@@ -875,7 +875,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>17300</v>
+        <v>19400</v>
       </c>
       <c r="E14" s="3">
         <v>4600</v>
@@ -905,7 +905,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>63200</v>
+        <v>67100</v>
       </c>
       <c r="E15" s="3">
         <v>40100</v>
@@ -946,7 +946,7 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>896800</v>
+        <v>894700</v>
       </c>
       <c r="E17" s="3">
         <v>692500</v>
@@ -976,7 +976,7 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>185800</v>
+        <v>187900</v>
       </c>
       <c r="E18" s="3">
         <v>185800</v>
@@ -1050,7 +1050,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>248300</v>
+        <v>254300</v>
       </c>
       <c r="E21" s="3">
         <v>225100</v>
